--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1077"/>
+  <dimension ref="A1:G1078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33813,6 +33813,37 @@
       </c>
       <c r="G1077" t="inlineStr"/>
     </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>05:19:32</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1078" t="n">
+        <v>2687</v>
+      </c>
+      <c r="G1078" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1078"/>
+  <dimension ref="A1:G1079"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33844,6 +33844,37 @@
       </c>
       <c r="G1078" t="inlineStr"/>
     </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>05:20:24</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1079" t="n">
+        <v>365</v>
+      </c>
+      <c r="G1079" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1079"/>
+  <dimension ref="A1:G1080"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33875,6 +33875,37 @@
       </c>
       <c r="G1079" t="inlineStr"/>
     </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>05:20:58</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1080" t="n">
+        <v>1668</v>
+      </c>
+      <c r="G1080" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1080"/>
+  <dimension ref="A1:G1081"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33906,6 +33906,37 @@
       </c>
       <c r="G1080" t="inlineStr"/>
     </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>05:21:24</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1081" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1081" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1081"/>
+  <dimension ref="A1:G1082"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33937,6 +33937,37 @@
       </c>
       <c r="G1081" t="inlineStr"/>
     </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>05:21:39</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1082" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1082" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1082"/>
+  <dimension ref="A1:G1083"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33968,6 +33968,37 @@
       </c>
       <c r="G1082" t="inlineStr"/>
     </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>05:21:56</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>اسطبه تدوير</t>
+        </is>
+      </c>
+      <c r="F1083" t="n">
+        <v>240</v>
+      </c>
+      <c r="G1083" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1083"/>
+  <dimension ref="A1:G1084"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33999,6 +33999,37 @@
       </c>
       <c r="G1083" t="inlineStr"/>
     </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>04:39:44</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1084" t="n">
+        <v>2648</v>
+      </c>
+      <c r="G1084" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1084"/>
+  <dimension ref="A1:G1085"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34030,6 +34030,37 @@
       </c>
       <c r="G1084" t="inlineStr"/>
     </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>04:41:21</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1085" t="n">
+        <v>1224</v>
+      </c>
+      <c r="G1085" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1085"/>
+  <dimension ref="A1:G1086"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34061,6 +34061,37 @@
       </c>
       <c r="G1085" t="inlineStr"/>
     </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>04:41:58</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1086" t="n">
+        <v>181</v>
+      </c>
+      <c r="G1086" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1086"/>
+  <dimension ref="A1:G1087"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34092,6 +34092,37 @@
       </c>
       <c r="G1086" t="inlineStr"/>
     </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>04:42:40</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>شراق غزل</t>
+        </is>
+      </c>
+      <c r="F1087" t="n">
+        <v>187</v>
+      </c>
+      <c r="G1087" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1087"/>
+  <dimension ref="A1:G1088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34123,6 +34123,37 @@
       </c>
       <c r="G1087" t="inlineStr"/>
     </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>04:43:14</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>محمود فتحيT.C</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1088" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1088" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1088"/>
+  <dimension ref="A1:G1089"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34154,6 +34154,37 @@
       </c>
       <c r="G1088" t="inlineStr"/>
     </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>20:02:56</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1089" t="n">
+        <v>1627</v>
+      </c>
+      <c r="G1089" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1089"/>
+  <dimension ref="A1:G1090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34185,6 +34185,37 @@
       </c>
       <c r="G1089" t="inlineStr"/>
     </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>20:03:15</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1090" t="n">
+        <v>361</v>
+      </c>
+      <c r="G1090" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1090"/>
+  <dimension ref="A1:G1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34216,6 +34216,37 @@
       </c>
       <c r="G1090" t="inlineStr"/>
     </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>20:03:27</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1091" t="n">
+        <v>3066</v>
+      </c>
+      <c r="G1091" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1091"/>
+  <dimension ref="A1:G1092"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34247,6 +34247,37 @@
       </c>
       <c r="G1091" t="inlineStr"/>
     </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>20:03:41</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>انفاق</t>
+        </is>
+      </c>
+      <c r="F1092" t="n">
+        <v>224</v>
+      </c>
+      <c r="G1092" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1092"/>
+  <dimension ref="A1:G1093"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34278,6 +34278,37 @@
       </c>
       <c r="G1092" t="inlineStr"/>
     </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>20:03:52</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>اسطبه تدوير</t>
+        </is>
+      </c>
+      <c r="F1093" t="n">
+        <v>215</v>
+      </c>
+      <c r="G1093" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1093"/>
+  <dimension ref="A1:G1094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34309,6 +34309,37 @@
       </c>
       <c r="G1093" t="inlineStr"/>
     </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>20:04:05</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1094" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1094" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1094"/>
+  <dimension ref="A1:G1095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34340,6 +34340,37 @@
       </c>
       <c r="G1094" t="inlineStr"/>
     </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>20:04:28</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1095" t="n">
+        <v>1428</v>
+      </c>
+      <c r="G1095" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1095"/>
+  <dimension ref="A1:G1096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34371,6 +34371,37 @@
       </c>
       <c r="G1095" t="inlineStr"/>
     </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>20:04:39</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1096" t="n">
+        <v>351</v>
+      </c>
+      <c r="G1096" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1096"/>
+  <dimension ref="A1:G1097"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34402,6 +34402,37 @@
       </c>
       <c r="G1096" t="inlineStr"/>
     </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>20:04:56</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1097" t="n">
+        <v>2469</v>
+      </c>
+      <c r="G1097" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1097"/>
+  <dimension ref="A1:G1098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34433,6 +34433,37 @@
       </c>
       <c r="G1097" t="inlineStr"/>
     </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>20:05:06</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1098" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1098" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1098"/>
+  <dimension ref="A1:G1099"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34464,6 +34464,37 @@
       </c>
       <c r="G1098" t="inlineStr"/>
     </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>20:05:22</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>هبوه دست</t>
+        </is>
+      </c>
+      <c r="F1099" t="n">
+        <v>221</v>
+      </c>
+      <c r="G1099" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1099"/>
+  <dimension ref="A1:G1100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34495,6 +34495,37 @@
       </c>
       <c r="G1099" t="inlineStr"/>
     </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>20:05:35</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>اسطبه تدوير</t>
+        </is>
+      </c>
+      <c r="F1100" t="n">
+        <v>220</v>
+      </c>
+      <c r="G1100" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1100"/>
+  <dimension ref="A1:G1101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34526,6 +34526,37 @@
       </c>
       <c r="G1100" t="inlineStr"/>
     </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>20:05:44</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1101" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1101" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1101"/>
+  <dimension ref="A1:G1102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34557,6 +34557,37 @@
       </c>
       <c r="G1101" t="inlineStr"/>
     </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>20:06:08</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1102" t="n">
+        <v>1456</v>
+      </c>
+      <c r="G1102" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1102"/>
+  <dimension ref="A1:G1103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34588,6 +34588,37 @@
       </c>
       <c r="G1102" t="inlineStr"/>
     </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>20:06:20</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1103" t="n">
+        <v>180</v>
+      </c>
+      <c r="G1103" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1103"/>
+  <dimension ref="A1:G1104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34619,6 +34619,37 @@
       </c>
       <c r="G1103" t="inlineStr"/>
     </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>20:06:32</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1104" t="n">
+        <v>2696</v>
+      </c>
+      <c r="G1104" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1104"/>
+  <dimension ref="A1:G1105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34650,6 +34650,37 @@
       </c>
       <c r="G1104" t="inlineStr"/>
     </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>20:06:45</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1105" t="n">
+        <v>175</v>
+      </c>
+      <c r="G1105" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1105"/>
+  <dimension ref="A1:G1106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34681,6 +34681,37 @@
       </c>
       <c r="G1105" t="inlineStr"/>
     </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>20:06:58</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>انفاق</t>
+        </is>
+      </c>
+      <c r="F1106" t="n">
+        <v>256</v>
+      </c>
+      <c r="G1106" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1106"/>
+  <dimension ref="A1:G1107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34712,6 +34712,37 @@
       </c>
       <c r="G1106" t="inlineStr"/>
     </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>20:07:13</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>اسطبه تدوير</t>
+        </is>
+      </c>
+      <c r="F1107" t="n">
+        <v>217</v>
+      </c>
+      <c r="G1107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1107"/>
+  <dimension ref="A1:G1108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34743,6 +34743,37 @@
       </c>
       <c r="G1107" t="inlineStr"/>
     </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>20:07:26</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1108" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1108" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1108"/>
+  <dimension ref="A1:G1109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34774,6 +34774,37 @@
       </c>
       <c r="G1108" t="inlineStr"/>
     </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>20:17:08</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1109" t="n">
+        <v>1445</v>
+      </c>
+      <c r="G1109" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1109"/>
+  <dimension ref="A1:G1110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34805,6 +34805,37 @@
       </c>
       <c r="G1109" t="inlineStr"/>
     </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>20:17:19</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1110" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1110" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1110"/>
+  <dimension ref="A1:G1111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34836,6 +34836,37 @@
       </c>
       <c r="G1110" t="inlineStr"/>
     </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>20:17:33</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1111" t="n">
+        <v>2694</v>
+      </c>
+      <c r="G1111" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1111"/>
+  <dimension ref="A1:G1112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34867,6 +34867,37 @@
       </c>
       <c r="G1111" t="inlineStr"/>
     </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>20:17:43</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>شراق غزل</t>
+        </is>
+      </c>
+      <c r="F1112" t="n">
+        <v>175</v>
+      </c>
+      <c r="G1112" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1112"/>
+  <dimension ref="A1:G1113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34898,6 +34898,37 @@
       </c>
       <c r="G1112" t="inlineStr"/>
     </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>20:17:52</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1113" t="n">
+        <v>205</v>
+      </c>
+      <c r="G1113" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1113"/>
+  <dimension ref="A1:G1114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34929,6 +34929,37 @@
       </c>
       <c r="G1113" t="inlineStr"/>
     </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>20:18:07</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>هبوه دست</t>
+        </is>
+      </c>
+      <c r="F1114" t="n">
+        <v>214</v>
+      </c>
+      <c r="G1114" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1114"/>
+  <dimension ref="A1:G1115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34960,6 +34960,37 @@
       </c>
       <c r="G1114" t="inlineStr"/>
     </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>20:18:23</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>اسطبه تدوير</t>
+        </is>
+      </c>
+      <c r="F1115" t="n">
+        <v>208</v>
+      </c>
+      <c r="G1115" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1115"/>
+  <dimension ref="A1:G1116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34991,6 +34991,37 @@
       </c>
       <c r="G1115" t="inlineStr"/>
     </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>20:18:33</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1116" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1116" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1116"/>
+  <dimension ref="A1:G1117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35022,6 +35022,37 @@
       </c>
       <c r="G1116" t="inlineStr"/>
     </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>23:27:14</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1117" t="n">
+        <v>1655</v>
+      </c>
+      <c r="G1117" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1117"/>
+  <dimension ref="A1:G1118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35053,6 +35053,37 @@
       </c>
       <c r="G1117" t="inlineStr"/>
     </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>23:27:30</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1118" t="n">
+        <v>361</v>
+      </c>
+      <c r="G1118" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1118"/>
+  <dimension ref="A1:G1119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35084,6 +35084,37 @@
       </c>
       <c r="G1118" t="inlineStr"/>
     </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>23:27:44</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1119" t="n">
+        <v>2890</v>
+      </c>
+      <c r="G1119" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1119"/>
+  <dimension ref="A1:G1120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35115,6 +35115,37 @@
       </c>
       <c r="G1119" t="inlineStr"/>
     </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>23:28:01</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>مكس2</t>
+        </is>
+      </c>
+      <c r="F1120" t="n">
+        <v>227</v>
+      </c>
+      <c r="G1120" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1120"/>
+  <dimension ref="A1:G1121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35146,6 +35146,37 @@
       </c>
       <c r="G1120" t="inlineStr"/>
     </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>23:28:17</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1121" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1121" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1121"/>
+  <dimension ref="A1:G1122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35177,6 +35177,37 @@
       </c>
       <c r="G1121" t="inlineStr"/>
     </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>23:19:38</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1122" t="n">
+        <v>1652</v>
+      </c>
+      <c r="G1122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1122"/>
+  <dimension ref="A1:G1123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35208,6 +35208,37 @@
       </c>
       <c r="G1122" t="inlineStr"/>
     </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>23:19:51</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1123" t="n">
+        <v>357</v>
+      </c>
+      <c r="G1123" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1123"/>
+  <dimension ref="A1:G1124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35239,6 +35239,37 @@
       </c>
       <c r="G1123" t="inlineStr"/>
     </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>23:20:07</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1124" t="n">
+        <v>2694</v>
+      </c>
+      <c r="G1124" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1124"/>
+  <dimension ref="A1:G1125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35270,6 +35270,37 @@
       </c>
       <c r="G1124" t="inlineStr"/>
     </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>23:20:24</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1125" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1125" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1125"/>
+  <dimension ref="A1:G1126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35301,6 +35301,37 @@
       </c>
       <c r="G1125" t="inlineStr"/>
     </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>23:20:41</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>اسطبه تدوير</t>
+        </is>
+      </c>
+      <c r="F1126" t="n">
+        <v>225</v>
+      </c>
+      <c r="G1126" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1126"/>
+  <dimension ref="A1:G1127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35332,6 +35332,37 @@
       </c>
       <c r="G1126" t="inlineStr"/>
     </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>23:20:50</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1127" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1127" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1127"/>
+  <dimension ref="A1:G1128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35363,6 +35363,37 @@
       </c>
       <c r="G1127" t="inlineStr"/>
     </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>04:18:25</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1128" t="n">
+        <v>1238</v>
+      </c>
+      <c r="G1128" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1128"/>
+  <dimension ref="A1:G1129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35394,6 +35394,37 @@
       </c>
       <c r="G1128" t="inlineStr"/>
     </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>04:18:35</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1129" t="n">
+        <v>186</v>
+      </c>
+      <c r="G1129" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1129"/>
+  <dimension ref="A1:G1130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35425,6 +35425,37 @@
       </c>
       <c r="G1129" t="inlineStr"/>
     </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>04:18:52</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1130" t="n">
+        <v>2697</v>
+      </c>
+      <c r="G1130" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1130"/>
+  <dimension ref="A1:G1131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35456,6 +35456,37 @@
       </c>
       <c r="G1130" t="inlineStr"/>
     </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>04:19:11</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>شراق غزل</t>
+        </is>
+      </c>
+      <c r="F1131" t="n">
+        <v>155</v>
+      </c>
+      <c r="G1131" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1131"/>
+  <dimension ref="A1:G1132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35487,6 +35487,37 @@
       </c>
       <c r="G1131" t="inlineStr"/>
     </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>04:19:22</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1132" t="n">
+        <v>205</v>
+      </c>
+      <c r="G1132" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1132"/>
+  <dimension ref="A1:G1133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35518,6 +35518,37 @@
       </c>
       <c r="G1132" t="inlineStr"/>
     </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>04:19:37</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1133" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1133" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1133"/>
+  <dimension ref="A1:G1134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35549,6 +35549,37 @@
       </c>
       <c r="G1133" t="inlineStr"/>
     </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>14:47:46</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1134" t="n">
+        <v>1225</v>
+      </c>
+      <c r="G1134" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1134"/>
+  <dimension ref="A1:G1135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35580,6 +35580,37 @@
       </c>
       <c r="G1134" t="inlineStr"/>
     </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>14:47:57</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1135" t="n">
+        <v>170</v>
+      </c>
+      <c r="G1135" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1135"/>
+  <dimension ref="A1:G1136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35611,6 +35611,37 @@
       </c>
       <c r="G1135" t="inlineStr"/>
     </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>14:48:09</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1136" t="n">
+        <v>2483</v>
+      </c>
+      <c r="G1136" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1136"/>
+  <dimension ref="A1:G1137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35642,6 +35642,37 @@
       </c>
       <c r="G1136" t="inlineStr"/>
     </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>14:48:18</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>شراق غزل</t>
+        </is>
+      </c>
+      <c r="F1137" t="n">
+        <v>205</v>
+      </c>
+      <c r="G1137" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1137"/>
+  <dimension ref="A1:G1138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35673,6 +35673,37 @@
       </c>
       <c r="G1137" t="inlineStr"/>
     </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>14:48:31</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1138" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1138" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1138"/>
+  <dimension ref="A1:G1139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35704,6 +35704,37 @@
       </c>
       <c r="G1138" t="inlineStr"/>
     </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>14:48:43</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>هبوه دست</t>
+        </is>
+      </c>
+      <c r="F1139" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1139" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1139"/>
+  <dimension ref="A1:G1140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35735,6 +35735,37 @@
       </c>
       <c r="G1139" t="inlineStr"/>
     </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>14:48:53</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1140" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1140" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1140"/>
+  <dimension ref="A1:G1141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35766,6 +35766,37 @@
       </c>
       <c r="G1140" t="inlineStr"/>
     </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>14:49:08</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1141" t="n">
+        <v>1434</v>
+      </c>
+      <c r="G1141" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1141"/>
+  <dimension ref="A1:G1142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35797,6 +35797,37 @@
       </c>
       <c r="G1141" t="inlineStr"/>
     </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>14:49:19</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1142" t="n">
+        <v>180</v>
+      </c>
+      <c r="G1142" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1142"/>
+  <dimension ref="A1:G1143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35828,6 +35828,37 @@
       </c>
       <c r="G1142" t="inlineStr"/>
     </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>14:49:34</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1143" t="n">
+        <v>2698</v>
+      </c>
+      <c r="G1143" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1143"/>
+  <dimension ref="A1:G1144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35859,6 +35859,37 @@
       </c>
       <c r="G1143" t="inlineStr"/>
     </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>14:49:45</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>شراق غزل</t>
+        </is>
+      </c>
+      <c r="F1144" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1144" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1144"/>
+  <dimension ref="A1:G1145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35890,6 +35890,37 @@
       </c>
       <c r="G1144" t="inlineStr"/>
     </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>14:49:54</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1145" t="n">
+        <v>206</v>
+      </c>
+      <c r="G1145" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1145"/>
+  <dimension ref="A1:G1146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35921,6 +35921,37 @@
       </c>
       <c r="G1145" t="inlineStr"/>
     </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>14:50:07</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>انفاق</t>
+        </is>
+      </c>
+      <c r="F1146" t="n">
+        <v>227</v>
+      </c>
+      <c r="G1146" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1146"/>
+  <dimension ref="A1:G1147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35952,6 +35952,37 @@
       </c>
       <c r="G1146" t="inlineStr"/>
     </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>14:50:21</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>اسطبه تدوير</t>
+        </is>
+      </c>
+      <c r="F1147" t="n">
+        <v>248</v>
+      </c>
+      <c r="G1147" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1147"/>
+  <dimension ref="A1:G1148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35983,6 +35983,37 @@
       </c>
       <c r="G1147" t="inlineStr"/>
     </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>14:50:30</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1148" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1148" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1148"/>
+  <dimension ref="A1:G1149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36014,6 +36014,37 @@
       </c>
       <c r="G1148" t="inlineStr"/>
     </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>23:09:04</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1149" t="n">
+        <v>1653</v>
+      </c>
+      <c r="G1149" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1149"/>
+  <dimension ref="A1:G1150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36045,6 +36045,37 @@
       </c>
       <c r="G1149" t="inlineStr"/>
     </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>23:09:17</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1150" t="n">
+        <v>352</v>
+      </c>
+      <c r="G1150" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1150"/>
+  <dimension ref="A1:G1151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36076,6 +36076,37 @@
       </c>
       <c r="G1150" t="inlineStr"/>
     </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>23:09:36</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1151" t="n">
+        <v>2891</v>
+      </c>
+      <c r="G1151" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1151"/>
+  <dimension ref="A1:G1152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36107,6 +36107,37 @@
       </c>
       <c r="G1151" t="inlineStr"/>
     </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>23:09:47</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>شراق غزل</t>
+        </is>
+      </c>
+      <c r="F1152" t="n">
+        <v>213</v>
+      </c>
+      <c r="G1152" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1152"/>
+  <dimension ref="A1:G1153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36138,6 +36138,37 @@
       </c>
       <c r="G1152" t="inlineStr"/>
     </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>23:10:08</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>مكس2</t>
+        </is>
+      </c>
+      <c r="F1153" t="n">
+        <v>224</v>
+      </c>
+      <c r="G1153" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1153"/>
+  <dimension ref="A1:G1154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36169,6 +36169,37 @@
       </c>
       <c r="G1153" t="inlineStr"/>
     </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>23:10:23</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1154" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1154" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1154"/>
+  <dimension ref="A1:G1155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36200,6 +36200,37 @@
       </c>
       <c r="G1154" t="inlineStr"/>
     </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>23:10:35</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>اسطبه تدوير</t>
+        </is>
+      </c>
+      <c r="F1155" t="n">
+        <v>211</v>
+      </c>
+      <c r="G1155" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1155"/>
+  <dimension ref="A1:G1156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36231,6 +36231,37 @@
       </c>
       <c r="G1155" t="inlineStr"/>
     </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>23:10:47</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1156" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1156" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1156"/>
+  <dimension ref="A1:G1157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36262,6 +36262,37 @@
       </c>
       <c r="G1156" t="inlineStr"/>
     </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>23:11:06</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1157" t="n">
+        <v>1855</v>
+      </c>
+      <c r="G1157" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1157"/>
+  <dimension ref="A1:G1158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36293,6 +36293,37 @@
       </c>
       <c r="G1157" t="inlineStr"/>
     </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>23:11:21</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1158" t="n">
+        <v>178</v>
+      </c>
+      <c r="G1158" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1158"/>
+  <dimension ref="A1:G1159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36324,6 +36324,37 @@
       </c>
       <c r="G1158" t="inlineStr"/>
     </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>23:11:33</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1159" t="n">
+        <v>2901</v>
+      </c>
+      <c r="G1159" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1159"/>
+  <dimension ref="A1:G1160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36355,6 +36355,37 @@
       </c>
       <c r="G1159" t="inlineStr"/>
     </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>23:11:53</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>مكس2</t>
+        </is>
+      </c>
+      <c r="F1160" t="n">
+        <v>214</v>
+      </c>
+      <c r="G1160" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1160"/>
+  <dimension ref="A1:G1161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36386,6 +36386,37 @@
       </c>
       <c r="G1160" t="inlineStr"/>
     </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>23:12:03</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1161" t="n">
+        <v>150</v>
+      </c>
+      <c r="G1161" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1161"/>
+  <dimension ref="A1:G1162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36417,6 +36417,37 @@
       </c>
       <c r="G1161" t="inlineStr"/>
     </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>23:12:13</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>هبوه دست</t>
+        </is>
+      </c>
+      <c r="F1162" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1162" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1162"/>
+  <dimension ref="A1:G1163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36448,6 +36448,37 @@
       </c>
       <c r="G1162" t="inlineStr"/>
     </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>23:12:23</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>الثانيه</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1163" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1163" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1163"/>
+  <dimension ref="A1:G1164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36479,6 +36479,37 @@
       </c>
       <c r="G1163" t="inlineStr"/>
     </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>02:43:35</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1164" t="n">
+        <v>1232</v>
+      </c>
+      <c r="G1164" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1164"/>
+  <dimension ref="A1:G1165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36510,6 +36510,37 @@
       </c>
       <c r="G1164" t="inlineStr"/>
     </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>02:43:57</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1165" t="n">
+        <v>178</v>
+      </c>
+      <c r="G1165" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1165"/>
+  <dimension ref="A1:G1166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36541,6 +36541,37 @@
       </c>
       <c r="G1165" t="inlineStr"/>
     </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>02:44:22</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1166" t="n">
+        <v>2688</v>
+      </c>
+      <c r="G1166" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1166"/>
+  <dimension ref="A1:G1167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36572,6 +36572,37 @@
       </c>
       <c r="G1166" t="inlineStr"/>
     </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>02:44:37</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>شراق غزل</t>
+        </is>
+      </c>
+      <c r="F1167" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1167" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1167"/>
+  <dimension ref="A1:G1168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36603,6 +36603,37 @@
       </c>
       <c r="G1167" t="inlineStr"/>
     </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>02:44:56</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1168" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1168" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1168"/>
+  <dimension ref="A1:G1169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36634,6 +36634,37 @@
       </c>
       <c r="G1168" t="inlineStr"/>
     </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>02:45:14</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>مكس2</t>
+        </is>
+      </c>
+      <c r="F1169" t="n">
+        <v>220</v>
+      </c>
+      <c r="G1169" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1169"/>
+  <dimension ref="A1:G1170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36665,6 +36665,37 @@
       </c>
       <c r="G1169" t="inlineStr"/>
     </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>02:45:33</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>اسطبه تدوير</t>
+        </is>
+      </c>
+      <c r="F1170" t="n">
+        <v>237</v>
+      </c>
+      <c r="G1170" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1170"/>
+  <dimension ref="A1:G1171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36696,6 +36696,37 @@
       </c>
       <c r="G1170" t="inlineStr"/>
     </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>02:45:44</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1171" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1171" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1171"/>
+  <dimension ref="A1:G1172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36727,6 +36727,37 @@
       </c>
       <c r="G1171" t="inlineStr"/>
     </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>11:22:26</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1172" t="n">
+        <v>1447</v>
+      </c>
+      <c r="G1172" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1172"/>
+  <dimension ref="A1:G1173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36758,6 +36758,37 @@
       </c>
       <c r="G1172" t="inlineStr"/>
     </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>11:22:44</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1173" t="n">
+        <v>363</v>
+      </c>
+      <c r="G1173" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1173"/>
+  <dimension ref="A1:G1174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36789,6 +36789,37 @@
       </c>
       <c r="G1173" t="inlineStr"/>
     </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1174" t="n">
+        <v>2891</v>
+      </c>
+      <c r="G1174" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1174"/>
+  <dimension ref="A1:G1175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36820,6 +36820,37 @@
       </c>
       <c r="G1174" t="inlineStr"/>
     </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>11:23:11</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1175" t="n">
+        <v>175</v>
+      </c>
+      <c r="G1175" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1175"/>
+  <dimension ref="A1:G1176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36851,6 +36851,37 @@
       </c>
       <c r="G1175" t="inlineStr"/>
     </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>11:23:24</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>هبوه دست</t>
+        </is>
+      </c>
+      <c r="F1176" t="n">
+        <v>224</v>
+      </c>
+      <c r="G1176" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1176"/>
+  <dimension ref="A1:G1177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36882,6 +36882,37 @@
       </c>
       <c r="G1176" t="inlineStr"/>
     </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>11:23:34</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1177" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1177" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1177"/>
+  <dimension ref="A1:G1178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36913,6 +36913,37 @@
       </c>
       <c r="G1177" t="inlineStr"/>
     </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>11:24:00</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1178" t="n">
+        <v>1439</v>
+      </c>
+      <c r="G1178" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1178"/>
+  <dimension ref="A1:G1179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36944,6 +36944,37 @@
       </c>
       <c r="G1178" t="inlineStr"/>
     </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>11:24:13</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1179" t="n">
+        <v>193</v>
+      </c>
+      <c r="G1179" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1179"/>
+  <dimension ref="A1:G1180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36975,6 +36975,37 @@
       </c>
       <c r="G1179" t="inlineStr"/>
     </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>11:24:27</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1180" t="n">
+        <v>2494</v>
+      </c>
+      <c r="G1180" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1180"/>
+  <dimension ref="A1:G1181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37006,6 +37006,37 @@
       </c>
       <c r="G1180" t="inlineStr"/>
     </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>11:24:37</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>شراق غزل</t>
+        </is>
+      </c>
+      <c r="F1181" t="n">
+        <v>209</v>
+      </c>
+      <c r="G1181" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1181"/>
+  <dimension ref="A1:G1182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37037,6 +37037,37 @@
       </c>
       <c r="G1181" t="inlineStr"/>
     </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>11:24:54</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1182" t="n">
+        <v>185</v>
+      </c>
+      <c r="G1182" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1182"/>
+  <dimension ref="A1:G1183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37068,6 +37068,37 @@
       </c>
       <c r="G1182" t="inlineStr"/>
     </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>11:25:19</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>هبوه دست</t>
+        </is>
+      </c>
+      <c r="F1183" t="n">
+        <v>234</v>
+      </c>
+      <c r="G1183" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1183"/>
+  <dimension ref="A1:G1184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37099,6 +37099,37 @@
       </c>
       <c r="G1183" t="inlineStr"/>
     </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>11:25:29</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>الاولي</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1184" t="n">
+        <v>180</v>
+      </c>
+      <c r="G1184" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1184"/>
+  <dimension ref="A1:G1185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37130,6 +37130,37 @@
       </c>
       <c r="G1184" t="inlineStr"/>
     </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>02:38:45</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1185" t="n">
+        <v>1491</v>
+      </c>
+      <c r="G1185" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1185"/>
+  <dimension ref="A1:G1186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37161,6 +37161,37 @@
       </c>
       <c r="G1185" t="inlineStr"/>
     </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>02:38:59</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1186" t="n">
+        <v>183</v>
+      </c>
+      <c r="G1186" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1186"/>
+  <dimension ref="A1:G1187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37192,6 +37192,37 @@
       </c>
       <c r="G1186" t="inlineStr"/>
     </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>02:39:11</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1187" t="n">
+        <v>2274</v>
+      </c>
+      <c r="G1187" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1187"/>
+  <dimension ref="A1:G1188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37223,6 +37223,37 @@
       </c>
       <c r="G1187" t="inlineStr"/>
     </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>02:39:26</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>انفاق</t>
+        </is>
+      </c>
+      <c r="F1188" t="n">
+        <v>233</v>
+      </c>
+      <c r="G1188" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1188"/>
+  <dimension ref="A1:G1189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37254,6 +37254,37 @@
       </c>
       <c r="G1188" t="inlineStr"/>
     </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>02:39:42</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>اسطبه تدوير</t>
+        </is>
+      </c>
+      <c r="F1189" t="n">
+        <v>207</v>
+      </c>
+      <c r="G1189" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1189"/>
+  <dimension ref="A1:G1190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37285,6 +37285,37 @@
       </c>
       <c r="G1189" t="inlineStr"/>
     </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>02:39:53</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1190" t="n">
+        <v>210</v>
+      </c>
+      <c r="G1190" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1190"/>
+  <dimension ref="A1:G1191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37316,6 +37316,37 @@
       </c>
       <c r="G1190" t="inlineStr"/>
     </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>02:41:02</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1191" t="n">
+        <v>1562</v>
+      </c>
+      <c r="G1191" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1191"/>
+  <dimension ref="A1:G1192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37347,6 +37347,37 @@
       </c>
       <c r="G1191" t="inlineStr"/>
     </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>02:41:12</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1192" t="n">
+        <v>221</v>
+      </c>
+      <c r="G1192" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1192"/>
+  <dimension ref="A1:G1193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37378,6 +37378,37 @@
       </c>
       <c r="G1192" t="inlineStr"/>
     </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>02:41:24</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1193" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G1193" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1193"/>
+  <dimension ref="A1:G1194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37409,6 +37409,37 @@
       </c>
       <c r="G1193" t="inlineStr"/>
     </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>02:41:43</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>انفاق</t>
+        </is>
+      </c>
+      <c r="F1194" t="n">
+        <v>249</v>
+      </c>
+      <c r="G1194" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1194"/>
+  <dimension ref="A1:G1195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37440,6 +37440,37 @@
       </c>
       <c r="G1194" t="inlineStr"/>
     </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>02:41:57</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1195" t="n">
+        <v>173</v>
+      </c>
+      <c r="G1195" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1195"/>
+  <dimension ref="A1:G1196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37471,6 +37471,37 @@
       </c>
       <c r="G1195" t="inlineStr"/>
     </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>02:42:06</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1196" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1196" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1196"/>
+  <dimension ref="A1:G1197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37502,6 +37502,37 @@
       </c>
       <c r="G1196" t="inlineStr"/>
     </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>02:42:35</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1197" t="n">
+        <v>1548</v>
+      </c>
+      <c r="G1197" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1197"/>
+  <dimension ref="A1:G1198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37533,6 +37533,37 @@
       </c>
       <c r="G1197" t="inlineStr"/>
     </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>02:42:43</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1198" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1198" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1198"/>
+  <dimension ref="A1:G1199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37564,6 +37564,37 @@
       </c>
       <c r="G1198" t="inlineStr"/>
     </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>02:42:55</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1199" t="n">
+        <v>2538</v>
+      </c>
+      <c r="G1199" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1199"/>
+  <dimension ref="A1:G1200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37595,6 +37595,37 @@
       </c>
       <c r="G1199" t="inlineStr"/>
     </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>02:43:08</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1200" t="n">
+        <v>150</v>
+      </c>
+      <c r="G1200" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1200"/>
+  <dimension ref="A1:G1201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37626,6 +37626,37 @@
       </c>
       <c r="G1200" t="inlineStr"/>
     </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>02:43:21</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>انفاق</t>
+        </is>
+      </c>
+      <c r="F1201" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1201" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1201"/>
+  <dimension ref="A1:G1202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37657,6 +37657,37 @@
       </c>
       <c r="G1201" t="inlineStr"/>
     </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>02:43:30</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1202" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1202" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1202"/>
+  <dimension ref="A1:G1203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37688,6 +37688,37 @@
       </c>
       <c r="G1202" t="inlineStr"/>
     </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>02:43:51</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>الكرد</t>
+        </is>
+      </c>
+      <c r="F1203" t="n">
+        <v>1358</v>
+      </c>
+      <c r="G1203" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1203"/>
+  <dimension ref="A1:G1204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37719,6 +37719,37 @@
       </c>
       <c r="G1203" t="inlineStr"/>
     </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>02:44:04</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>مكس</t>
+        </is>
+      </c>
+      <c r="F1204" t="n">
+        <v>224</v>
+      </c>
+      <c r="G1204" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1204"/>
+  <dimension ref="A1:G1205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37750,6 +37750,37 @@
       </c>
       <c r="G1204" t="inlineStr"/>
     </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>02:44:20</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>تمشيط غير مغلف</t>
+        </is>
+      </c>
+      <c r="F1205" t="n">
+        <v>2355</v>
+      </c>
+      <c r="G1205" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1205"/>
+  <dimension ref="A1:G1206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37781,6 +37781,37 @@
       </c>
       <c r="G1205" t="inlineStr"/>
     </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>02:44:33</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>شراق غزل</t>
+        </is>
+      </c>
+      <c r="F1206" t="n">
+        <v>212</v>
+      </c>
+      <c r="G1206" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1206"/>
+  <dimension ref="A1:G1207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37812,6 +37812,37 @@
       </c>
       <c r="G1206" t="inlineStr"/>
     </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>02:44:48</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>شراق برم وملفات</t>
+        </is>
+      </c>
+      <c r="F1207" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1207" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/luva.xlsx
+++ b/luva.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1207"/>
+  <dimension ref="A1:G1208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37843,6 +37843,37 @@
       </c>
       <c r="G1207" t="inlineStr"/>
     </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>02:45:01</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>الثالثه</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>احمد عبالعزيزT.D</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>تراب</t>
+        </is>
+      </c>
+      <c r="F1208" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1208" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
